--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-as-vs-type-fermeture.xlsx
+++ b/main/ig/ValueSet-as-vs-type-fermeture.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
